--- a/files/week-09-resource-studio.xlsx
+++ b/files/week-09-resource-studio.xlsx
@@ -11756,13 +11756,13 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F14"/>
+  <dimension ref="A1:F15"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="26" customWidth="1" min="1" max="1"/>
-    <col width="12" customWidth="1" min="2" max="2"/>
-    <col width="12" customWidth="1" min="3" max="3"/>
-    <col width="12" customWidth="1" min="4" max="4"/>
+    <col width="14" customWidth="1" min="2" max="2"/>
+    <col width="14" customWidth="1" min="3" max="3"/>
+    <col width="14" customWidth="1" min="4" max="4"/>
     <col width="46" customWidth="1" min="5" max="5"/>
     <col width="28" customWidth="1" min="6" max="6"/>
   </cols>
@@ -11770,14 +11770,14 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>AI levelling · reconciliation</t>
+          <t>AI against the notebook · reconciliation</t>
         </is>
       </c>
     </row>
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>Gemini levels the two-coordinator case cold. Compare its schedule with yours and with the optimum, line by line.</t>
+          <t>Gemini levels the two-coordinator case cold. Enter its values beside the Colab notebook's optimum, line by line; the notebook is the reference.</t>
         </is>
       </c>
     </row>
@@ -11789,7 +11789,7 @@
       </c>
       <c r="B4" s="3" t="inlineStr">
         <is>
-          <t>Your value</t>
+          <t>Your value (Part 2)</t>
         </is>
       </c>
       <c r="C4" s="3" t="inlineStr">
@@ -11799,7 +11799,7 @@
       </c>
       <c r="D4" s="3" t="inlineStr">
         <is>
-          <t>Optimum</t>
+          <t>Notebook optimum</t>
         </is>
       </c>
       <c r="E4" s="3" t="inlineStr">
@@ -11912,7 +11912,7 @@
     <row r="13" ht="36" customHeight="1">
       <c r="A13" s="19" t="inlineStr">
         <is>
-          <t>Where it put the five-day loan</t>
+          <t>Claims shortest possible? True?</t>
         </is>
       </c>
       <c r="B13" s="15" t="n"/>
@@ -11924,7 +11924,7 @@
     <row r="14" ht="36" customHeight="1">
       <c r="A14" s="19" t="inlineStr">
         <is>
-          <t>Other</t>
+          <t>Which of the three does it match?</t>
         </is>
       </c>
       <c r="B14" s="15" t="n"/>
@@ -11933,6 +11933,18 @@
       <c r="E14" s="15" t="n"/>
       <c r="F14" s="15" t="n"/>
     </row>
+    <row r="15" ht="36" customHeight="1">
+      <c r="A15" s="19" t="inlineStr">
+        <is>
+          <t>Other</t>
+        </is>
+      </c>
+      <c r="B15" s="15" t="n"/>
+      <c r="C15" s="15" t="n"/>
+      <c r="D15" s="15" t="n"/>
+      <c r="E15" s="15" t="n"/>
+      <c r="F15" s="15" t="n"/>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
